--- a/src/nodes/HPC/compressor_stage_5_blade_rotor_coordinates_foil.xlsx
+++ b/src/nodes/HPC/compressor_stage_5_blade_rotor_coordinates_foil.xlsx
@@ -357,7 +357,7 @@
         <v>0.00092234669050442327</v>
       </c>
       <c r="B2">
-        <v>0.00099566854325176335</v>
+        <v>0.00094106561917390143</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -365,7 +365,7 @@
         <v>0.0018446933810088466</v>
       </c>
       <c r="B3">
-        <v>0.0014728378364641413</v>
+        <v>0.0013975743465189804</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -373,7 +373,7 @@
         <v>0.00276704007151327</v>
       </c>
       <c r="B4">
-        <v>0.0018698568341209525</v>
+        <v>0.0017786551933638751</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -381,7 +381,7 @@
         <v>0.0036893867620176931</v>
       </c>
       <c r="B5">
-        <v>0.0022111221986577377</v>
+        <v>0.0021070814919688387</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -389,7 +389,7 @@
         <v>0.0046117334525221159</v>
       </c>
       <c r="B6">
-        <v>0.0025065979691275666</v>
+        <v>0.0023921559355262016</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -397,7 +397,7 @@
         <v>0.00553408014302654</v>
       </c>
       <c r="B7">
-        <v>0.0027619819187308576</v>
+        <v>0.0026391991272909088</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -405,7 +405,7 @@
         <v>0.0064564268335309634</v>
       </c>
       <c r="B8">
-        <v>0.0029806342775228522</v>
+        <v>0.0028513498439769378</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -413,7 +413,7 @@
         <v>0.0073787735240353862</v>
       </c>
       <c r="B9">
-        <v>0.0031677903307158316</v>
+        <v>0.0030334966525783873</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -421,7 +421,7 @@
         <v>0.0083011202145398082</v>
       </c>
       <c r="B10">
-        <v>0.0033290991393021417</v>
+        <v>0.003190914184899508</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -429,7 +429,7 @@
         <v>0.0092234669050442319</v>
       </c>
       <c r="B11">
-        <v>0.0034699898122373556</v>
+        <v>0.00332867154170503</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -437,7 +437,7 @@
         <v>0.010145813595548656</v>
       </c>
       <c r="B12">
-        <v>0.0035933685367900013</v>
+        <v>0.0034494829780144071</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -445,7 +445,7 @@
         <v>0.011068160286053079</v>
       </c>
       <c r="B13">
-        <v>0.0036922697655171976</v>
+        <v>0.0035468488969055082</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -453,7 +453,7 @@
         <v>0.011990506976557501</v>
       </c>
       <c r="B14">
-        <v>0.0037625327860901009</v>
+        <v>0.0036168874277315668</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -461,7 +461,7 @@
         <v>0.012912853667061927</v>
       </c>
       <c r="B15">
-        <v>0.0038210879613474152</v>
+        <v>0.0036754014568888605</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -469,7 +469,7 @@
         <v>0.013835200357566347</v>
       </c>
       <c r="B16">
-        <v>0.0038834636986192494</v>
+        <v>0.0037368852756254</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -477,7 +477,7 @@
         <v>0.014757547048070772</v>
       </c>
       <c r="B17">
-        <v>0.0039384895080337825</v>
+        <v>0.0037909140375530751</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -485,7 +485,7 @@
         <v>0.015679893738575194</v>
       </c>
       <c r="B18">
-        <v>0.0039717362237343323</v>
+        <v>0.0038240213313672634</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -493,7 +493,7 @@
         <v>0.016602240429079616</v>
       </c>
       <c r="B19">
-        <v>0.0039824388731266869</v>
+        <v>0.003835493623733408</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -501,7 +501,7 @@
         <v>0.017524587119584042</v>
       </c>
       <c r="B20">
-        <v>0.0039732485319322573</v>
+        <v>0.0038278056008094656</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -509,7 +509,7 @@
         <v>0.018446933810088464</v>
       </c>
       <c r="B21">
-        <v>0.0039468162758724513</v>
+        <v>0.0038034319487533961</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -517,7 +517,7 @@
         <v>0.019369280500592889</v>
       </c>
       <c r="B22">
-        <v>0.0039053206580599515</v>
+        <v>0.0037644062185685791</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -525,7 +525,7 @@
         <v>0.020291627191097311</v>
       </c>
       <c r="B23">
-        <v>0.0038490501411725274</v>
+        <v>0.0037109974206400828</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -533,7 +533,7 @@
         <v>0.021213973881601737</v>
       </c>
       <c r="B24">
-        <v>0.0037778206652792218</v>
+        <v>0.0036430334301983986</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -541,7 +541,7 @@
         <v>0.022136320572106159</v>
       </c>
       <c r="B25">
-        <v>0.0036914481704490771</v>
+        <v>0.0035603421224740168</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -549,7 +549,7 @@
         <v>0.023058667262610581</v>
       </c>
       <c r="B26">
-        <v>0.0035896695959337379</v>
+        <v>0.0034626775277990284</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -557,7 +557,7 @@
         <v>0.023981013953115003</v>
       </c>
       <c r="B27">
-        <v>0.003471905877715249</v>
+        <v>0.0033494982969119215</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -565,7 +565,7 @@
         <v>0.024903360643619428</v>
       </c>
       <c r="B28">
-        <v>0.0033374989509582565</v>
+        <v>0.0032201892356527842</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -573,7 +573,7 @@
         <v>0.025825707334123853</v>
       </c>
       <c r="B29">
-        <v>0.003185790750827408</v>
+        <v>0.0030741351498617051</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -581,7 +581,7 @@
         <v>0.026748054024628275</v>
       </c>
       <c r="B30">
-        <v>0.0030164727673530657</v>
+        <v>0.0029110469818617486</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -589,7 +589,7 @@
         <v>0.027670400715132694</v>
       </c>
       <c r="B31">
-        <v>0.002830634710028459</v>
+        <v>0.0027319402199078848</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -597,7 +597,7 @@
         <v>0.028592747405637119</v>
       </c>
       <c r="B32">
-        <v>0.0026297158432125292</v>
+        <v>0.0025381564887380593</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -605,7 +605,7 @@
         <v>0.029515094096141545</v>
       </c>
       <c r="B33">
-        <v>0.0024151554312642222</v>
+        <v>0.0023310374130902185</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -613,7 +613,7 @@
         <v>0.030437440786645967</v>
       </c>
       <c r="B34">
-        <v>0.002187824033222192</v>
+        <v>0.0021113937009260026</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -621,7 +621,7 @@
         <v>0.031359787477150389</v>
       </c>
       <c r="B35">
-        <v>0.0019463173868439375</v>
+        <v>0.0018779123931018267</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -629,7 +629,7 @@
         <v>0.032282134167654811</v>
       </c>
       <c r="B36">
-        <v>0.0016886625245666679</v>
+        <v>0.0016287496136978016</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -637,7 +637,7 @@
         <v>0.033204480858159233</v>
       </c>
       <c r="B37">
-        <v>0.0014128864788275901</v>
+        <v>0.0013620614867940343</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -645,7 +645,7 @@
         <v>0.034126827548663662</v>
       </c>
       <c r="B38">
-        <v>0.0011156239209702051</v>
+        <v>0.0010747044804427642</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -653,7 +653,7 @@
         <v>0.035049174239168084</v>
       </c>
       <c r="B39">
-        <v>0.00078794007796317562</v>
+        <v>0.00075833643858474564</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -661,7 +661,7 @@
         <v>0.035971520929672506</v>
       </c>
       <c r="B40">
-        <v>0.00041950781568145533</v>
+        <v>0.00040331554913286246</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -669,7 +669,7 @@
         <v>0.036893867620176928</v>
       </c>
       <c r="B41">
-        <v>-1.2800131656060298E-19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -685,7 +685,7 @@
         <v>0.035971520929672506</v>
       </c>
       <c r="B43">
-        <v>-6.6260180776330516E-05</v>
+        <v>-5.0067914227737588E-05</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -693,7 +693,7 @@
         <v>0.035049174239168084</v>
       </c>
       <c r="B44">
-        <v>-0.00010016910338972163</v>
+        <v>-7.0565464011291656E-05</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -701,7 +701,7 @@
         <v>0.034126827548663662</v>
       </c>
       <c r="B45">
-        <v>-0.00011195929485302229</v>
+        <v>-7.1039854325581357E-05</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -709,7 +709,7 @@
         <v>0.033204480858159233</v>
       </c>
       <c r="B46">
-        <v>-0.00011186328217908184</v>
+        <v>-6.1038290145526116E-05</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -717,7 +717,7 @@
         <v>0.032282134167654811</v>
       </c>
       <c r="B47">
-        <v>-0.00010872480149931189</v>
+        <v>-4.8811890630445889E-05</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -725,7 +725,7 @@
         <v>0.031359787477150389</v>
       </c>
       <c r="B48">
-        <v>-0.00010583242541937305</v>
+        <v>-3.742743167726264E-05</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -733,7 +733,7 @@
         <v>0.030437440786645967</v>
       </c>
       <c r="B49">
-        <v>-0.00010508593566348812</v>
+        <v>-2.8655603367298652E-05</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -741,7 +741,7 @@
         <v>0.029515094096141545</v>
       </c>
       <c r="B50">
-        <v>-0.00010838511395587993</v>
+        <v>-2.4267095781876381E-05</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -749,7 +749,7 @@
         <v>0.028592747405637119</v>
       </c>
       <c r="B51">
-        <v>-0.00011706479102156858</v>
+        <v>-2.550543654709854E-05</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -757,7 +757,7 @@
         <v>0.027670400715132694</v>
       </c>
       <c r="B52">
-        <v>-0.00013019999358876308</v>
+        <v>-3.1505503468188964E-05</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -765,7 +765,7 @@
         <v>0.026748054024628275</v>
       </c>
       <c r="B53">
-        <v>-0.0001463007973864696</v>
+        <v>-4.0875011895151765E-05</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -773,7 +773,7 @@
         <v>0.025825707334123853</v>
       </c>
       <c r="B54">
-        <v>-0.00016387727814369456</v>
+        <v>-5.2221677177991179E-05</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -781,7 +781,7 @@
         <v>0.024903360643619428</v>
       </c>
       <c r="B55">
-        <v>-0.000181792508205926</v>
+        <v>-6.4482792900453286E-05</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -789,7 +789,7 @@
         <v>0.023981013953115003</v>
       </c>
       <c r="B56">
-        <v>-0.00020032154638457961</v>
+        <v>-7.7913965581251983E-05</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -797,7 +797,7 @@
         <v>0.023058667262610581</v>
       </c>
       <c r="B57">
-        <v>-0.00022009244810755298</v>
+        <v>-9.3100379972843188E-05</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -805,7 +805,7 @@
         <v>0.022136320572106159</v>
       </c>
       <c r="B58">
-        <v>-0.00024173326880274354</v>
+        <v>-0.00011062722082768269</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -813,7 +813,7 @@
         <v>0.021213973881601737</v>
       </c>
       <c r="B59">
-        <v>-0.00026579638714548006</v>
+        <v>-0.00013100915206465651</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -821,7 +821,7 @@
         <v>0.020291627191097311</v>
       </c>
       <c r="B60">
-        <v>-0.00029253147480081521</v>
+        <v>-0.00015447875426837025</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -829,7 +829,7 @@
         <v>0.019369280500592889</v>
       </c>
       <c r="B61">
-        <v>-0.00032211252668123258</v>
+        <v>-0.00018119808718985956</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -837,7 +837,7 @@
         <v>0.018446933810088464</v>
       </c>
       <c r="B62">
-        <v>-0.00035471353769921593</v>
+        <v>-0.00021132921058016014</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -845,7 +845,7 @@
         <v>0.017524587119584042</v>
       </c>
       <c r="B63">
-        <v>-0.00039003940175148273</v>
+        <v>-0.00024459647062869116</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -853,7 +853,7 @@
         <v>0.016602240429079616</v>
       </c>
       <c r="B64">
-        <v>-0.00042591860867168593</v>
+        <v>-0.00027897335927840663</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -861,7 +861,7 @@
         <v>0.015679893738575194</v>
       </c>
       <c r="B65">
-        <v>-0.00045971054727771219</v>
+        <v>-0.00031199565491064391</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -869,7 +869,7 @@
         <v>0.014757547048070772</v>
       </c>
       <c r="B66">
-        <v>-0.00048877460638744837</v>
+        <v>-0.00034119913590674054</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -877,7 +877,7 @@
         <v>0.013835200357566347</v>
       </c>
       <c r="B67">
-        <v>-0.00051388899119623457</v>
+        <v>-0.000367310568202385</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -885,7 +885,7 @@
         <v>0.012912853667061927</v>
       </c>
       <c r="B68">
-        <v>-0.00054950717240922434</v>
+        <v>-0.00040382066795066954</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -893,7 +893,7 @@
         <v>0.011990506976557501</v>
       </c>
       <c r="B69">
-        <v>-0.00060682796466592992</v>
+        <v>-0.00046118260630739549</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -901,7 +901,7 @@
         <v>0.011068160286053079</v>
       </c>
       <c r="B70">
-        <v>-0.00067035629283348325</v>
+        <v>-0.00052493542422179379</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -909,7 +909,7 @@
         <v>0.010145813595548656</v>
       </c>
       <c r="B71">
-        <v>-0.00072319822647781316</v>
+        <v>-0.00057931266770221927</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -917,7 +917,7 @@
         <v>0.0092234669050442319</v>
       </c>
       <c r="B72">
-        <v>-0.000769558303732415</v>
+        <v>-0.00062824003320008912</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -925,7 +925,7 @@
         <v>0.0083011202145398082</v>
       </c>
       <c r="B73">
-        <v>-0.00081644949277686414</v>
+        <v>-0.00067826453837423043</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -933,7 +933,7 @@
         <v>0.0073787735240353862</v>
       </c>
       <c r="B74">
-        <v>-0.0008610200134074893</v>
+        <v>-0.00072672633527004515</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -941,7 +941,7 @@
         <v>0.0064564268335309634</v>
       </c>
       <c r="B75">
-        <v>-0.00089789872885459132</v>
+        <v>-0.00076861429530867642</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -949,7 +949,7 @@
         <v>0.00553408014302654</v>
       </c>
       <c r="B76">
-        <v>-0.00092150182446760684</v>
+        <v>-0.00079871903302765779</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -957,7 +957,7 @@
         <v>0.0046117334525221159</v>
       </c>
       <c r="B77">
-        <v>-0.00092666303891337728</v>
+        <v>-0.00081222100531201224</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -965,7 +965,7 @@
         <v>0.0036893867620176931</v>
       </c>
       <c r="B78">
-        <v>-0.00091009900200922952</v>
+        <v>-0.00080605829532033049</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -973,7 +973,7 @@
         <v>0.00276704007151327</v>
       </c>
       <c r="B79">
-        <v>-0.00086619238859136829</v>
+        <v>-0.00077499074783429094</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -981,7 +981,7 @@
         <v>0.0018446933810088466</v>
       </c>
       <c r="B80">
-        <v>-0.00078506686189068595</v>
+        <v>-0.000709803371945525</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -989,7 +989,7 @@
         <v>0.00092234669050442327</v>
       </c>
       <c r="B81">
-        <v>-0.00064241917908409215</v>
+        <v>-0.00058781625500623034</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1023,7 +1023,7 @@
         <v>0.0010687302769374866</v>
       </c>
       <c r="B2">
-        <v>0.00049567203457220811</v>
+        <v>0.00038653329869135214</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1031,7 +1031,7 @@
         <v>0.0021374605538749731</v>
       </c>
       <c r="B3">
-        <v>0.000740353720588551</v>
+        <v>0.00058991924680683045</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1039,7 +1039,7 @@
         <v>0.00320619083081246</v>
       </c>
       <c r="B4">
-        <v>0.00094566029742614943</v>
+        <v>0.00076336911154947643</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1047,7 +1047,7 @@
         <v>0.0042749211077499462</v>
       </c>
       <c r="B5">
-        <v>0.0011233540704523259</v>
+        <v>0.00091540053316582976</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1055,7 +1055,7 @@
         <v>0.0053436513846874326</v>
       </c>
       <c r="B6">
-        <v>0.001278230379072215</v>
+        <v>0.0010494869721975754</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1063,7 +1063,7 @@
         <v>0.00641238166162492</v>
       </c>
       <c r="B7">
-        <v>0.0014130261307924179</v>
+        <v>0.0011676114598387093</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1071,7 +1071,7 @@
         <v>0.0074811119385624061</v>
       </c>
       <c r="B8">
-        <v>0.0015293503182972222</v>
+        <v>0.0012709403542785663</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1079,7 +1079,7 @@
         <v>0.0085498422154998924</v>
       </c>
       <c r="B9">
-        <v>0.0016297185915584915</v>
+        <v>0.001361296295202872</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1087,7 +1087,7 @@
         <v>0.00961857249243738</v>
       </c>
       <c r="B10">
-        <v>0.0017168470361103754</v>
+        <v>0.0014406469699792697</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1095,7 +1095,7 @@
         <v>0.010687302769374865</v>
       </c>
       <c r="B11">
-        <v>0.0017933468224485979</v>
+        <v>0.0015108839752066847</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1103,7 +1103,7 @@
         <v>0.011756033046312352</v>
       </c>
       <c r="B12">
-        <v>0.0018606116906791973</v>
+        <v>0.0015730174223963062</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1111,7 +1111,7 @@
         <v>0.01282476332324984</v>
       </c>
       <c r="B13">
-        <v>0.0019152705743878972</v>
+        <v>0.0016246075734770982</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1119,7 +1119,7 @@
         <v>0.013893493600187325</v>
       </c>
       <c r="B14">
-        <v>0.0019553071905800065</v>
+        <v>0.001664195486095129</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1127,7 +1127,7 @@
         <v>0.014962223877124812</v>
       </c>
       <c r="B15">
-        <v>0.0019888891964594865</v>
+        <v>0.001697695250347105</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1135,7 +1135,7 @@
         <v>0.016030954154062298</v>
       </c>
       <c r="B16">
-        <v>0.0020235079269698133</v>
+        <v>0.0017305312400409884</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1143,7 +1143,7 @@
         <v>0.017099684430999785</v>
       </c>
       <c r="B17">
-        <v>0.0020537654878138678</v>
+        <v>0.0017587959313791217</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1151,7 +1151,7 @@
         <v>0.018168414707937272</v>
       </c>
       <c r="B18">
-        <v>0.0020726914011992745</v>
+        <v>0.0017774431723547905</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1159,7 +1159,7 @@
         <v>0.019237144984874759</v>
       </c>
       <c r="B19">
-        <v>0.0020799140845932326</v>
+        <v>0.0017862041957306726</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1167,7 +1167,7 @@
         <v>0.020305875261812247</v>
       </c>
       <c r="B20">
-        <v>0.0020767116792778356</v>
+        <v>0.0017860045804617929</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1175,7 +1175,7 @@
         <v>0.02137460553874973</v>
       </c>
       <c r="B21">
-        <v>0.0020643623265351766</v>
+        <v>0.001777769905503177</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1183,7 +1183,7 @@
         <v>0.022443335815687217</v>
       </c>
       <c r="B22">
-        <v>0.0020439166195531894</v>
+        <v>0.0017622609380457742</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1191,7 +1191,7 @@
         <v>0.023512066092624705</v>
       </c>
       <c r="B23">
-        <v>0.0020155149591431758</v>
+        <v>0.001739579198224232</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1199,7 +1199,7 @@
         <v>0.024580796369562192</v>
       </c>
       <c r="B24">
-        <v>0.00197907019802228</v>
+        <v>0.001709661394409122</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1207,7 +1207,7 @@
         <v>0.025649526646499679</v>
       </c>
       <c r="B25">
-        <v>0.0019344951889076439</v>
+        <v>0.0016724442349710155</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1215,7 +1215,7 @@
         <v>0.026718256923437163</v>
       </c>
       <c r="B26">
-        <v>0.0018816652120190686</v>
+        <v>0.0016278371612840159</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1223,7 +1223,7 @@
         <v>0.02778698720037465</v>
       </c>
       <c r="B27">
-        <v>0.0018203052575869803</v>
+        <v>0.0015756405467363516</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1231,7 +1231,7 @@
         <v>0.028855717477312137</v>
       </c>
       <c r="B28">
-        <v>0.0017501027433444632</v>
+        <v>0.0015156274977197832</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1239,7 +1239,7 @@
         <v>0.029924447754249624</v>
       </c>
       <c r="B29">
-        <v>0.0016707450870246</v>
+        <v>0.0014475711206260711</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1247,7 +1247,7 @@
         <v>0.030993178031187112</v>
       </c>
       <c r="B30">
-        <v>0.0015820890642005744</v>
+        <v>0.001371367071705053</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1255,7 +1255,7 @@
         <v>0.032061908308124595</v>
       </c>
       <c r="B31">
-        <v>0.0014846688818059689</v>
+        <v>0.001287401206638876</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1263,7 +1263,7 @@
         <v>0.033130638585062086</v>
       </c>
       <c r="B32">
-        <v>0.0013791881046144655</v>
+        <v>0.0011961819309677635</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1271,7 +1271,7 @@
         <v>0.03419936886199957</v>
       </c>
       <c r="B33">
-        <v>0.0012663502973997457</v>
+        <v>0.0010982176502319404</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1279,7 +1279,7 @@
         <v>0.03526809913893706</v>
       </c>
       <c r="B34">
-        <v>0.0011465851166355913</v>
+        <v>0.00099381839231391968</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1287,7 +1287,7 @@
         <v>0.036336829415874544</v>
       </c>
       <c r="B35">
-        <v>0.0010192265855961771</v>
+        <v>0.00088250067446537259</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1295,7 +1295,7 @@
         <v>0.037405559692812028</v>
       </c>
       <c r="B36">
-        <v>0.00088333481925577829</v>
+        <v>0.00076358263628026021</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1303,7 +1303,7 @@
         <v>0.038474289969749519</v>
       </c>
       <c r="B37">
-        <v>0.00073796993258866829</v>
+        <v>0.00063638241735254175</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1311,7 +1311,7 @@
         <v>0.039543020246687</v>
       </c>
       <c r="B38">
-        <v>0.00058152045491070663</v>
+        <v>0.00049973186780594711</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1319,7 +1319,7 @@
         <v>0.040611750523624493</v>
       </c>
       <c r="B39">
-        <v>0.00040968857290409191</v>
+        <v>0.00035051767988328195</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1327,7 +1327,7 @@
         <v>0.041680480800561977</v>
       </c>
       <c r="B40">
-        <v>0.00021750488759260758</v>
+        <v>0.00018514025635712041</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -1343,7 +1343,7 @@
         <v>0.04274921107749946</v>
       </c>
       <c r="B42">
-        <v>3.7971244177616674E-17</v>
+        <v>3.7968926738240559E-17</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -1351,7 +1351,7 @@
         <v>0.041680480800561977</v>
       </c>
       <c r="B43">
-        <v>-1.7021425708023657E-05</v>
+        <v>1.5343205527463458E-05</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -1359,7 +1359,7 @@
         <v>0.040611750523624493</v>
       </c>
       <c r="B44">
-        <v>-1.9086014203226906E-05</v>
+        <v>4.0084878817583082E-05</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -1367,7 +1367,7 @@
         <v>0.039543020246687</v>
       </c>
       <c r="B45">
-        <v>-1.1150466138275277E-05</v>
+        <v>7.0638120966484209E-05</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -1375,7 +1375,7 @@
         <v>0.038474289969749519</v>
       </c>
       <c r="B46">
-        <v>1.8285178341276202E-06</v>
+        <v>0.0001034160330702542</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -1383,7 +1383,7 @@
         <v>0.037405559692812028</v>
       </c>
       <c r="B47">
-        <v>1.5565377404197409E-05</v>
+        <v>0.00013531756037971556</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -1391,7 +1391,7 @@
         <v>0.036336829415874544</v>
       </c>
       <c r="B48">
-        <v>2.8459113633826635E-05</v>
+        <v>0.00016518502476463098</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -1399,7 +1399,7 @@
         <v>0.03526809913893706</v>
       </c>
       <c r="B49">
-        <v>3.9579867927827246E-05</v>
+        <v>0.00019234659224949869</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -1407,7 +1407,7 @@
         <v>0.03419936886199957</v>
       </c>
       <c r="B50">
-        <v>4.7997781691011028E-05</v>
+        <v>0.00021613042885881644</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -1415,7 +1415,7 @@
         <v>0.033130638585062086</v>
       </c>
       <c r="B51">
-        <v>5.3056411522423893E-05</v>
+        <v>0.0002360625851691256</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -1423,7 +1423,7 @@
         <v>0.032061908308124595</v>
       </c>
       <c r="B52">
-        <v>5.5192974798048057E-05</v>
+        <v>0.00025246064996514109</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -1431,7 +1431,7 @@
         <v>0.030993178031187112</v>
       </c>
       <c r="B53">
-        <v>5.511810408809983E-05</v>
+        <v>0.00026584009658362124</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -1439,7 +1439,7 @@
         <v>0.029924447754249624</v>
       </c>
       <c r="B54">
-        <v>5.3542431962795513E-05</v>
+        <v>0.00027671639836132449</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -1447,7 +1447,7 @@
         <v>0.028855717477312137</v>
       </c>
       <c r="B55">
-        <v>5.1006760556926E-05</v>
+        <v>0.00028548200618160605</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -1455,7 +1455,7 @@
         <v>0.02778698720037465</v>
       </c>
       <c r="B56">
-        <v>4.737257026358064E-05</v>
+        <v>0.0002920372811142098</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -1463,7 +1463,7 @@
         <v>0.026718256923437163</v>
       </c>
       <c r="B57">
-        <v>4.233151104042337E-05</v>
+        <v>0.00029615956177547645</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -1471,7 +1471,7 @@
         <v>0.025649526646499679</v>
       </c>
       <c r="B58">
-        <v>3.5575232845118164E-05</v>
+        <v>0.00029762618678174675</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -1479,7 +1479,7 @@
         <v>0.024580796369562192</v>
       </c>
       <c r="B59">
-        <v>2.683249068055637E-05</v>
+        <v>0.00029624129429371417</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -1487,7 +1487,7 @@
         <v>0.023512066092624705</v>
       </c>
       <c r="B60">
-        <v>1.5980459730539132E-05</v>
+        <v>0.000291916220649483</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -1495,7 +1495,7 @@
         <v>0.022443335815687217</v>
       </c>
       <c r="B61">
-        <v>2.9334202240950623E-06</v>
+        <v>0.00028458910173151</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -1503,7 +1503,7 @@
         <v>0.02137460553874973</v>
       </c>
       <c r="B62">
-        <v>-1.2394347609747258E-05</v>
+        <v>0.00027419807342225213</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -1511,7 +1511,7 @@
         <v>0.020305875261812247</v>
       </c>
       <c r="B63">
-        <v>-2.9861500548561988E-05</v>
+        <v>0.00026084559826748086</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -1519,7 +1519,7 @@
         <v>0.019237144984874759</v>
       </c>
       <c r="B64">
-        <v>-4.841844339633453E-05</v>
+        <v>0.00024529144546622572</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -1527,7 +1527,7 @@
         <v>0.018168414707937272</v>
       </c>
       <c r="B65">
-        <v>-6.6788517963652937E-05</v>
+        <v>0.000228459710880831</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -1535,7 +1535,7 @@
         <v>0.017099684430999785</v>
       </c>
       <c r="B66">
-        <v>-8.36950660611054E-05</v>
+        <v>0.00021127449037364087</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -1543,7 +1543,7 @@
         <v>0.016030954154062298</v>
       </c>
       <c r="B67">
-        <v>-9.9511543528920307E-05</v>
+        <v>0.00019346514339990491</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -1551,7 +1551,7 @@
         <v>0.014962223877124812</v>
       </c>
       <c r="B68">
-        <v>-0.00012121186232588736</v>
+        <v>0.00016998208378649421</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -1559,7 +1559,7 @@
         <v>0.013893493600187325</v>
       </c>
       <c r="B69">
-        <v>-0.00015419791438287455</v>
+        <v>0.000136913790102003</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -1567,7 +1567,7 @@
         <v>0.01282476332324984</v>
       </c>
       <c r="B70">
-        <v>-0.00019098305540050131</v>
+        <v>9.9679945510297734E-05</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -1575,7 +1575,7 @@
         <v>0.011756033046312352</v>
       </c>
       <c r="B71">
-        <v>-0.00022340474615334678</v>
+        <v>6.418952212954429E-05</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -1583,7 +1583,7 @@
         <v>0.010687302769374865</v>
       </c>
       <c r="B72">
-        <v>-0.00025348540394207637</v>
+        <v>2.8977443299836642E-05</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -1591,7 +1591,7 @@
         <v>0.00961857249243738</v>
       </c>
       <c r="B73">
-        <v>-0.00028460271846285183</v>
+        <v>-8.4026523317465647E-06</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -1599,7 +1599,7 @@
         <v>0.0085498422154998924</v>
       </c>
       <c r="B74">
-        <v>-0.00031537051246773441</v>
+        <v>-4.69482161121153E-05</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -1607,7 +1607,7 @@
         <v>0.0074811119385624061</v>
       </c>
       <c r="B75">
-        <v>-0.00034318565285245935</v>
+        <v>-8.4775688833803325E-05</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -1615,7 +1615,7 @@
         <v>0.00641238166162492</v>
       </c>
       <c r="B76">
-        <v>-0.00036534105003155966</v>
+        <v>-0.00011992637907785076</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1623,7 +1623,7 @@
         <v>0.0053436513846874326</v>
       </c>
       <c r="B77">
-        <v>-0.000379330540309232</v>
+        <v>-0.0001505871334345923</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1631,7 +1631,7 @@
         <v>0.0042749211077499462</v>
       </c>
       <c r="B78">
-        <v>-0.00038355562002952994</v>
+        <v>-0.0001756020827430338</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1639,7 +1639,7 @@
         <v>0.00320619083081246</v>
       </c>
       <c r="B79">
-        <v>-0.00037529032486858393</v>
+        <v>-0.0001929991389919108</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1647,7 +1647,7 @@
         <v>0.0021374605538749731</v>
       </c>
       <c r="B80">
-        <v>-0.00034975116188768509</v>
+        <v>-0.0001993166881059646</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1655,7 +1655,7 @@
         <v>0.0010687302769374866</v>
       </c>
       <c r="B81">
-        <v>-0.0002951883703615318</v>
+        <v>-0.00018604963448067574</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1689,7 +1689,7 @@
         <v>0.0011990506976557501</v>
       </c>
       <c r="B2">
-        <v>0.00033542056439864664</v>
+        <v>0.00024669081277212113</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1697,7 +1697,7 @@
         <v>0.0023981013953115003</v>
       </c>
       <c r="B3">
-        <v>0.00050181087073966038</v>
+        <v>0.00037950769957877388</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1705,7 +1705,7 @@
         <v>0.0035971520929672508</v>
       </c>
       <c r="B4">
-        <v>0.00064161987375826492</v>
+        <v>0.00049341720752801421</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1713,7 +1713,7 @@
         <v>0.0047962027906230005</v>
       </c>
       <c r="B5">
-        <v>0.00076276294500743813</v>
+        <v>0.00059369679663797738</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1721,7 +1721,7 @@
         <v>0.0059952534882787506</v>
       </c>
       <c r="B6">
-        <v>0.00086846569320023594</v>
+        <v>0.00068249738859801825</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1729,7 +1729,7 @@
         <v>0.0071943041859345016</v>
       </c>
       <c r="B7">
-        <v>0.00096056825344858284</v>
+        <v>0.00076104621735866582</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1737,7 +1737,7 @@
         <v>0.0083933548835902518</v>
       </c>
       <c r="B8">
-        <v>0.0010401515838890654</v>
+        <v>0.00083006437937695361</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1745,7 +1745,7 @@
         <v>0.009592405581246001</v>
       </c>
       <c r="B9">
-        <v>0.0011089071794082408</v>
+        <v>0.0008906799524348941</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1753,7 +1753,7 @@
         <v>0.010791456278901752</v>
       </c>
       <c r="B10">
-        <v>0.0011686615623474549</v>
+        <v>0.00094411101144317527</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1761,7 +1761,7 @@
         <v>0.011990506976557501</v>
       </c>
       <c r="B11">
-        <v>0.0012211708281172371</v>
+        <v>0.000991528638502208</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1769,7 +1769,7 @@
         <v>0.013189557674213252</v>
       </c>
       <c r="B12">
-        <v>0.0012673716401157653</v>
+        <v>0.0010335576071054255</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1777,7 +1777,7 @@
         <v>0.014388608371869003</v>
       </c>
       <c r="B13">
-        <v>0.0013049933606226255</v>
+        <v>0.0010686844491286302</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1785,7 +1785,7 @@
         <v>0.015587659069524753</v>
       </c>
       <c r="B14">
-        <v>0.001332677443544864</v>
+        <v>0.0010960037362122458</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1793,7 +1793,7 @@
         <v>0.016786709767180504</v>
       </c>
       <c r="B15">
-        <v>0.0013559210104179642</v>
+        <v>0.0011191804406728127</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1801,7 +1801,7 @@
         <v>0.017985760464836253</v>
       </c>
       <c r="B16">
-        <v>0.0013797659949713697</v>
+        <v>0.0011415760576063642</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1809,7 +1809,7 @@
         <v>0.019184811162492002</v>
       </c>
       <c r="B17">
-        <v>0.0014005779120819331</v>
+        <v>0.0011607677725507829</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1817,7 +1817,7 @@
         <v>0.020383861860147755</v>
       </c>
       <c r="B18">
-        <v>0.001413663786010702</v>
+        <v>0.0011736270859142163</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1825,7 +1825,7 @@
         <v>0.021582912557803504</v>
       </c>
       <c r="B19">
-        <v>0.0014187730974080939</v>
+        <v>0.0011799870671440154</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1833,7 +1833,7 @@
         <v>0.022781963255459253</v>
       </c>
       <c r="B20">
-        <v>0.0014167659410218687</v>
+        <v>0.0011804211779473325</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1841,7 +1841,7 @@
         <v>0.023981013953115003</v>
       </c>
       <c r="B21">
-        <v>0.0014085024115997858</v>
+        <v>0.0011755028800313205</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1849,7 +1849,7 @@
         <v>0.025180064650770755</v>
       </c>
       <c r="B22">
-        <v>0.0013946895260592749</v>
+        <v>0.0011657035618857941</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1857,7 +1857,7 @@
         <v>0.026379115348426505</v>
       </c>
       <c r="B23">
-        <v>0.0013754219899964411</v>
+        <v>0.0011510863191312182</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1865,7 +1865,7 @@
         <v>0.027578166046082257</v>
       </c>
       <c r="B24">
-        <v>0.0013506414311770592</v>
+        <v>0.0011316121741707212</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1873,7 +1873,7 @@
         <v>0.028777216743738007</v>
       </c>
       <c r="B25">
-        <v>0.0013202894773669039</v>
+        <v>0.00110724214940743</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1881,7 +1881,7 @@
         <v>0.029976267441393752</v>
       </c>
       <c r="B26">
-        <v>0.0012842825596647873</v>
+        <v>0.001077920448945884</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1889,7 +1889,7 @@
         <v>0.031175318139049505</v>
       </c>
       <c r="B27">
-        <v>0.0012424363225016718</v>
+        <v>0.0010435240036962643</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1897,7 +1897,7 @@
         <v>0.032374368836705254</v>
       </c>
       <c r="B28">
-        <v>0.0011945412136415573</v>
+        <v>0.0010039129262701641</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1905,7 +1905,7 @@
         <v>0.033573419534361007</v>
       </c>
       <c r="B29">
-        <v>0.0011403876808484437</v>
+        <v>0.00095894732927917579</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1913,7 +1913,7 @@
         <v>0.03477247023201676</v>
       </c>
       <c r="B30">
-        <v>0.0010798802745654011</v>
+        <v>0.00090856337314200962</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1921,7 +1921,7 @@
         <v>0.035971520929672506</v>
       </c>
       <c r="B31">
-        <v>0.0010133799559517785</v>
+        <v>0.00085300140950584551</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1929,7 +1929,7 @@
         <v>0.037170571627328258</v>
       </c>
       <c r="B32">
-        <v>0.00094136178884599432</v>
+        <v>0.00079257783782498066</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1937,7 +1937,7 @@
         <v>0.038369622324984004</v>
       </c>
       <c r="B33">
-        <v>0.00086430083708646777</v>
+        <v>0.00072760905755371217</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1945,7 +1945,7 @@
         <v>0.039568673022639757</v>
       </c>
       <c r="B34">
-        <v>0.00078248788132073222</v>
+        <v>0.00065828859133942451</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1953,7 +1953,7 @@
         <v>0.04076772372029551</v>
       </c>
       <c r="B35">
-        <v>0.00069547656943277881</v>
+        <v>0.00058431845460184945</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1961,7 +1961,7 @@
         <v>0.041966774417951255</v>
       </c>
       <c r="B36">
-        <v>0.00060263626611571316</v>
+        <v>0.00050527778595380588</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1969,7 +1969,7 @@
         <v>0.043165825115607008</v>
       </c>
       <c r="B37">
-        <v>0.00050333633606264013</v>
+        <v>0.000420745724008112</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1977,7 +1977,7 @@
         <v>0.044364875813262754</v>
       </c>
       <c r="B38">
-        <v>0.00039649414955490958</v>
+        <v>0.000330000058697818</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1985,7 +1985,7 @@
         <v>0.045563926510918507</v>
       </c>
       <c r="B39">
-        <v>0.00027921909922684645</v>
+        <v>0.00023111318523689784</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1993,7 +1993,7 @@
         <v>0.046762977208574259</v>
       </c>
       <c r="B40">
-        <v>0.00014816858330102002</v>
+        <v>0.00012185615015955662</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2009,7 +2009,7 @@
         <v>0.047962027906230005</v>
       </c>
       <c r="B42">
-        <v>-2.6000267426372481E-21</v>
+        <v>5.2000534852744961E-21</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -2017,7 +2017,7 @@
         <v>0.046762977208574259</v>
       </c>
       <c r="B43">
-        <v>-9.7060155477604E-06</v>
+        <v>1.6606417593703022E-05</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2025,7 +2025,7 @@
         <v>0.045563926510918507</v>
       </c>
       <c r="B44">
-        <v>-9.4163847128451591E-06</v>
+        <v>3.8689529277103463E-05</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2033,7 +2033,7 @@
         <v>0.044364875813262754</v>
       </c>
       <c r="B45">
-        <v>-2.4703955876393857E-06</v>
+        <v>6.4023695269452125E-05</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2041,7 +2041,7 @@
         <v>0.043165825115607008</v>
       </c>
       <c r="B46">
-        <v>7.792663735471745E-06</v>
+        <v>9.0383275789999838E-05</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2049,7 +2049,7 @@
         <v>0.041966774417951255</v>
       </c>
       <c r="B47">
-        <v>1.8485385144269752E-05</v>
+        <v>0.00011584386530617701</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2057,7 +2057,7 @@
         <v>0.04076772372029551</v>
       </c>
       <c r="B48">
-        <v>2.8527880447202869E-05</v>
+        <v>0.0001396859952781322</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -2065,7 +2065,7 @@
         <v>0.039568673022639757</v>
       </c>
       <c r="B49">
-        <v>3.7292141432886176E-05</v>
+        <v>0.00016149143141419388</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -2073,7 +2073,7 @@
         <v>0.038369622324984004</v>
       </c>
       <c r="B50">
-        <v>4.4150159889934615E-05</v>
+        <v>0.00018084193942269016</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -2081,7 +2081,7 @@
         <v>0.037170571627328258</v>
       </c>
       <c r="B51">
-        <v>4.865808271991247E-05</v>
+        <v>0.00019744203374092613</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -2089,7 +2089,7 @@
         <v>0.035971520929672506</v>
       </c>
       <c r="B52">
-        <v>5.1108677276181304E-05</v>
+        <v>0.00021148722372211422</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -2097,7 +2097,7 @@
         <v>0.03477247023201676</v>
       </c>
       <c r="B53">
-        <v>5.1978866025052014E-05</v>
+        <v>0.00022329576744844356</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -2105,7 +2105,7 @@
         <v>0.033573419534361007</v>
       </c>
       <c r="B54">
-        <v>5.1745571432835458E-05</v>
+        <v>0.00023318592300210355</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -2113,7 +2113,7 @@
         <v>0.032374368836705254</v>
       </c>
       <c r="B55">
-        <v>5.0771489413197962E-05</v>
+        <v>0.00024139977678459126</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -2121,7 +2121,7 @@
         <v>0.031175318139049505</v>
       </c>
       <c r="B56">
-        <v>4.8962409669227581E-05</v>
+        <v>0.00024787472847463503</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -2129,7 +2129,7 @@
         <v>0.029976267441393752</v>
       </c>
       <c r="B57">
-        <v>4.6109895351367783E-05</v>
+        <v>0.00025247200607027113</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -2137,7 +2137,7 @@
         <v>0.028777216743738007</v>
       </c>
       <c r="B58">
-        <v>4.2005509610062071E-05</v>
+        <v>0.00025505283756953578</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -2145,7 +2145,7 @@
         <v>0.027578166046082257</v>
       </c>
       <c r="B59">
-        <v>3.646588913903115E-05</v>
+        <v>0.00025549514614536925</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -2153,7 +2153,7 @@
         <v>0.026379115348426505</v>
       </c>
       <c r="B60">
-        <v>2.9407964805104808E-05</v>
+        <v>0.00025374363567032764</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -2161,7 +2161,7 @@
         <v>0.025180064650770755</v>
       </c>
       <c r="B61">
-        <v>2.0773741018390054E-05</v>
+        <v>0.00024975970519187094</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -2169,7 +2169,7 @@
         <v>0.023981013953115003</v>
       </c>
       <c r="B62">
-        <v>1.0505222188993926E-05</v>
+        <v>0.00024350475375745935</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -2177,7 +2177,7 @@
         <v>0.022781963255459253</v>
       </c>
       <c r="B63">
-        <v>-1.3026374253469002E-06</v>
+        <v>0.00023504212564918911</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -2185,7 +2185,7 @@
         <v>0.021582912557803504</v>
       </c>
       <c r="B64">
-        <v>-1.3943084176377245E-05</v>
+        <v>0.00022484294608770137</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -2193,7 +2193,7 @@
         <v>0.020383861860147755</v>
       </c>
       <c r="B65">
-        <v>-2.6556414568212205E-05</v>
+        <v>0.00021348028552827357</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -2201,7 +2201,7 @@
         <v>0.019184811162492002</v>
       </c>
       <c r="B66">
-        <v>-3.8282925104966987E-05</v>
+        <v>0.00020152721442618309</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -2209,7 +2209,7 @@
         <v>0.017985760464836253</v>
       </c>
       <c r="B67">
-        <v>-4.93736292186626E-05</v>
+        <v>0.00018881630814634282</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -2217,7 +2217,7 @@
         <v>0.016786709767180504</v>
       </c>
       <c r="B68">
-        <v>-6.4522408052943651E-05</v>
+        <v>0.00017221816169220772</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -2225,7 +2225,7 @@
         <v>0.015587659069524753</v>
       </c>
       <c r="B69">
-        <v>-8.7364800450845932E-05</v>
+        <v>0.00014930890688177244</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -2233,7 +2233,7 @@
         <v>0.014388608371869003</v>
       </c>
       <c r="B70">
-        <v>-0.00011286010834134582</v>
+        <v>0.00012344880315264944</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -2241,7 +2241,7 @@
         <v>0.013189557674213252</v>
       </c>
       <c r="B71">
-        <v>-0.00013551255794627418</v>
+        <v>9.830147506406581E-05</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -2249,7 +2249,7 @@
         <v>0.011990506976557501</v>
       </c>
       <c r="B72">
-        <v>-0.0001566823095729383</v>
+        <v>7.2959880042090989E-05</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -2257,7 +2257,7 @@
         <v>0.010791456278901752</v>
       </c>
       <c r="B73">
-        <v>-0.00017864174307822197</v>
+        <v>4.5908807826057541E-05</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -2265,7 +2265,7 @@
         <v>0.009592405581246001</v>
       </c>
       <c r="B74">
-        <v>-0.00020045618243183844</v>
+        <v>1.7771044541508187E-05</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -2273,7 +2273,7 @@
         <v>0.0083933548835902518</v>
       </c>
       <c r="B75">
-        <v>-0.00022037164318360395</v>
+        <v>-1.0284438671492291E-05</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -2281,7 +2281,7 @@
         <v>0.0071943041859345016</v>
       </c>
       <c r="B76">
-        <v>-0.00023656396309091821</v>
+        <v>-3.7041927001001243E-05</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -2289,7 +2289,7 @@
         <v>0.0059952534882787506</v>
       </c>
       <c r="B77">
-        <v>-0.00024734413441307061</v>
+        <v>-6.1375829810852723E-05</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -2297,7 +2297,7 @@
         <v>0.0047962027906230005</v>
       </c>
       <c r="B78">
-        <v>-0.00025163394520932625</v>
+        <v>-8.2567796839865478E-05</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -2305,7 +2305,7 @@
         <v>0.0035971520929672508</v>
       </c>
       <c r="B79">
-        <v>-0.00024759612362323935</v>
+        <v>-9.9393457392988626E-05</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -2313,7 +2313,7 @@
         <v>0.0023981013953115003</v>
       </c>
       <c r="B80">
-        <v>-0.00023200815622565849</v>
+        <v>-0.00010970498506477201</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -2321,7 +2321,7 @@
         <v>0.0011990506976557501</v>
       </c>
       <c r="B81">
-        <v>-0.00019695794536050637</v>
+        <v>-0.00010822819373398087</v>
       </c>
     </row>
     <row r="82" spans="1:2">
